--- a/metadata/EndpointMetadata_Ver_1_1.xlsx
+++ b/metadata/EndpointMetadata_Ver_1_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/degn400/Git_Repos/srpAnalytics/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E191587-F8EE-DF47-BAA8-F2311FB194C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D4FDD4-2135-D245-BACE-41EAE9A0889D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="149">
   <si>
     <t>Abbreviation</t>
   </si>
@@ -444,9 +444,6 @@
     <t>Measurement of the amount of ruptured cells in response to a chemical, as ruptured cells release lactate dehydrogenase.</t>
   </si>
   <si>
-    <t>DCDFA</t>
-  </si>
-  <si>
     <t>Reactive Oxygen Species Detection</t>
   </si>
   <si>
@@ -466,6 +463,15 @@
   </si>
   <si>
     <t>EndpointType</t>
+  </si>
+  <si>
+    <t>DCFDA</t>
+  </si>
+  <si>
+    <t>NC24</t>
+  </si>
+  <si>
+    <t>Notochord malformation at 24 hours</t>
   </si>
 </sst>
 </file>
@@ -811,7 +817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0498EF9C-E9A3-468C-A290-DEE17D385575}">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="2"/>
@@ -829,7 +835,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>29</v>
@@ -849,7 +855,7 @@
         <v>84</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>63</v>
@@ -866,13 +872,13 @@
         <v>127</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -883,7 +889,7 @@
         <v>23</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>64</v>
@@ -900,7 +906,7 @@
         <v>109</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>65</v>
@@ -914,7 +920,7 @@
         <v>128</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>65</v>
@@ -934,7 +940,7 @@
         <v>93</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -945,7 +951,7 @@
         <v>94</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -956,7 +962,7 @@
         <v>95</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -967,7 +973,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>115</v>
@@ -987,7 +993,7 @@
         <v>43</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>32</v>
@@ -1004,7 +1010,7 @@
         <v>129</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>6</v>
@@ -1024,7 +1030,7 @@
         <v>132</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>133</v>
@@ -1042,7 +1048,7 @@
         <v>14</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>113</v>
@@ -1062,7 +1068,7 @@
         <v>17</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>114</v>
@@ -1079,7 +1085,7 @@
         <v>10</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>9</v>
@@ -1096,16 +1102,16 @@
         <v>91</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -1116,7 +1122,7 @@
         <v>2</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>66</v>
@@ -1136,7 +1142,7 @@
         <v>12</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>11</v>
@@ -1156,7 +1162,7 @@
         <v>48</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>116</v>
@@ -1176,7 +1182,7 @@
         <v>49</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>117</v>
@@ -1193,7 +1199,7 @@
         <v>136</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>137</v>
@@ -1210,7 +1216,7 @@
         <v>13</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>112</v>
@@ -1230,7 +1236,7 @@
         <v>130</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>131</v>
@@ -1247,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>69</v>
@@ -1267,7 +1273,7 @@
         <v>4</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>70</v>
@@ -1287,7 +1293,7 @@
         <v>110</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>88</v>
@@ -1301,7 +1307,7 @@
         <v>25</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>88</v>
@@ -1315,42 +1321,37 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>79</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="F29" s="3"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>92</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -1358,13 +1359,19 @@
         <v>92</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>111</v>
+        <v>67</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -1372,19 +1379,13 @@
         <v>92</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -1392,19 +1393,19 @@
         <v>92</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -1412,56 +1413,59 @@
         <v>92</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>27</v>
+        <v>125</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>118</v>
+        <v>27</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>41</v>
+        <v>28</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
@@ -1469,19 +1473,16 @@
         <v>92</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
@@ -1489,19 +1490,19 @@
         <v>92</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
@@ -1509,16 +1510,19 @@
         <v>92</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>107</v>
+        <v>37</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -1526,16 +1530,16 @@
         <v>92</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
@@ -1543,16 +1547,16 @@
         <v>92</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>106</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
@@ -1560,16 +1564,16 @@
         <v>92</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -1577,16 +1581,16 @@
         <v>92</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>97</v>
+        <v>18</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
@@ -1594,21 +1598,38 @@
         <v>92</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D44" s="2" t="s">
+      <c r="C45" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E45" s="2" t="s">
         <v>105</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F36">
-    <sortCondition ref="B2:B36"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F37">
+    <sortCondition ref="B2:B37"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="F19" r:id="rId1" xr:uid="{F4F80936-7DCC-48C0-940B-84C684D4BFC4}"/>
@@ -1624,15 +1645,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100396ED2E7A640164CB8C59FDEC2C765CC" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="26e8590940edae28bea0b080f6fa8b06">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="aceb4bc4-7be6-4130-8e8a-7008d72bfcc3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7a9331905dac936d9e88b896f6b901d6" ns3:_="">
     <xsd:import namespace="aceb4bc4-7be6-4130-8e8a-7008d72bfcc3"/>
@@ -1802,21 +1814,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49E57FCB-AF0B-40B5-9F88-8BBFA3B90FEE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8D080FC-E009-4447-ACD6-B9CB0ED3D7DD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1834,7 +1847,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{565D9DA6-2D7C-4976-B32E-584E4A2A7F7C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -1848,4 +1861,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49E57FCB-AF0B-40B5-9F88-8BBFA3B90FEE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>